--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260731.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260731.xlsx
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>700,000</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>300,000</t>
+          <t>700,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1701,12 +1701,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
